--- a/brain/library/internal/scorecard/Behavioral Health Practice Management Scorecard April 2026.xlsx
+++ b/brain/library/internal/scorecard/Behavioral Health Practice Management Scorecard April 2026.xlsx
@@ -837,7 +837,7 @@
     <row r="3">
       <c r="B3" s="61" t="inlineStr">
         <is>
-          <t>XX Initial Screen</t>
+          <t>Behavioral Health Practice Management Initial Screen</t>
         </is>
       </c>
     </row>
@@ -869,13 +869,21 @@
           <t>Margins</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>15%+ EBITDA margins required</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Vertical SaaS gross margins 70-80%; mature platforms EBITDA 25-35%. Sub-scale bootstrapped targets likely 15-25% pre-synergy. Above 15% threshold.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -883,13 +891,21 @@
           <t>Recurring Revenue</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Existing recurring/contractual revenue or clear path to convert</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Per-provider SaaS subscriptions ($29-99/provider/mo). 90%+ recurring revenue typical. NRR 105-115% from seat expansion in group practices.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -897,13 +913,21 @@
           <t>Industry Growth</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Growth rate above GDP (~3%+)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>US behavioral health software growing ~10-12% CAGR — well above GDP. Telehealth normalization, parity enforcement, measurement-based care tailwinds.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -911,13 +935,21 @@
           <t>Growth TAM</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>$500M+ total addressable market (investor floor)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>US behavioral health PM/EHR TAM est. $800M-$1.2B, above $500M investor floor. Broader behavioral health services market ~$80B provides headroom.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="62" t="inlineStr">
@@ -925,10 +957,19 @@
           <t>VERDICT</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>All 4 must pass to proceed to Industry Scorecard</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>All 4 criteria pass. Proceed to Industry Scorecard. PE saturation is scoring concern, not a gate.</t>
         </is>
       </c>
     </row>
@@ -945,10 +986,19 @@
           <t>Number of independently owned acquisition candidates</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15-25</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>Determines sprint duration, not go/no-go</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Est. 15-25 independent PM/EHR vendors remain (most major incumbents PE-owned). Specialty-vertical and clinician-founder tools are the primary pool.</t>
         </is>
       </c>
     </row>
@@ -958,10 +1008,19 @@
           <t>Sprint duration estimate</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Fast</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>50+ = long sprint | 20-50 = focused | 10-20 = fast | &lt;10 = very fast</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>15-25 targets. Fast sprint.</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1066,7 @@
     <row r="3" customFormat="1" s="28">
       <c r="B3" s="33" t="inlineStr">
         <is>
-          <t>XX Industry Scorecard</t>
+          <t>Behavioral Health Practice Management Industry Scorecard</t>
         </is>
       </c>
       <c r="C3" s="30" t="n"/>
@@ -1028,7 +1087,7 @@
     <row r="5" ht="14.5" customHeight="1">
       <c r="B5" s="35" t="inlineStr">
         <is>
-          <t>XX  Industry Scorecard</t>
+          <t>Behavioral Health Practice Management Industry Scorecard</t>
         </is>
       </c>
       <c r="C5" s="36" t="inlineStr">
@@ -1158,7 +1217,7 @@
       </c>
       <c r="J9" s="23" t="inlineStr">
         <is>
-          <t>&gt;10% industry growth</t>
+          <t>~10-12% CAGR for behavioral health software — roughly 3-4x GDP. Telehealth + parity + measurement-based care expansion.</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1234,7 @@
       </c>
       <c r="E10" s="48" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -1200,7 +1259,7 @@
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t>Data 'manipulation' is a huge pain point</t>
+          <t>Moderate digital penetration; many solo/small group practices still on generic EHRs or paper. Specialty workflows underserved. Catalyst present but not urgent.</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1295,11 @@
           <t>Mostly Headwinds</t>
         </is>
       </c>
-      <c r="J11" s="23" t="n"/>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>Mostly tailwinds: parity enforcement, telehealth normalization, VBC, measurement-based care mandates. AI-native entrants a minor headwind for general category.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
       <c r="B12" s="19" t="inlineStr">
@@ -1251,7 +1314,7 @@
       </c>
       <c r="E12" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F12" s="21" t="n"/>
@@ -1272,7 +1335,7 @@
       </c>
       <c r="J12" s="24" t="inlineStr">
         <is>
-          <t>Data 'manipulation' is a huge pain point</t>
+          <t>Strong catalysts: 988 rollout, parity enforcement, CMS measurement-based care, employer mental health investment, state VBC pilots.</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1391,7 @@
       </c>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t>~7 well-known players</t>
+          <t>10-15 notable vendors; dozens of smaller specialty tools. Concentrated at top, long tail at bottom.</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1429,7 @@
       </c>
       <c r="J15" s="24" t="inlineStr">
         <is>
-          <t>Largest has ~35% of market</t>
+          <t>SimplePractice + TherapyNotes + Qualifacts/Netsmart together ~50-55% share. No single player &gt;25%. Specialty mid-market fragmented.</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1485,7 @@
       </c>
       <c r="J17" s="23" t="inlineStr">
         <is>
-          <t>~80%/~55% recurring/non-rec gross margin</t>
+          <t>Vertical SaaS gross margins 70-80%. Software delivery cost minimal; some services layer for onboarding/compliance.</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1502,7 @@
       </c>
       <c r="E18" s="48" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F18" s="9" t="n"/>
@@ -1460,7 +1523,7 @@
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>Probably close to 30%</t>
+          <t>Mature platforms 25-35% EBITDA; sub-scale bootstrapped targets 15-25%. Expansion opportunity but not yet at 30%+ avg.</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1561,7 @@
       </c>
       <c r="J19" s="24" t="inlineStr">
         <is>
-          <t>Probably close to 20%</t>
+          <t>Asset-light SaaS. Minimal capex. Vertical SaaS typically &gt;20% ROTC.</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1596,7 @@
       </c>
       <c r="E21" s="48" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F21" s="9" t="n"/>
@@ -1554,7 +1617,7 @@
       </c>
       <c r="J21" s="23" t="inlineStr">
         <is>
-          <t>Outstanding customer feedback</t>
+          <t>SimplePractice/TherapyNotes highly rated; Valant/Qualifacts mixed. Specialty tools get strong NPS from niche buyers.</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1634,7 @@
       </c>
       <c r="E22" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F22" s="9" t="n"/>
@@ -1592,7 +1655,7 @@
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>Weaker value proposition</t>
+          <t>Clear value: HIPAA-compliant clinical notes, claim scrubbing, telehealth, measurement-based care. System of record between clinician and payer.</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1672,7 @@
       </c>
       <c r="E23" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F23" s="21" t="n"/>
@@ -1630,7 +1693,7 @@
       </c>
       <c r="J23" s="24" t="inlineStr">
         <is>
-          <t>Can be replaced w/effort</t>
+          <t>High switching costs: holds every clinical note, claim, ERA, credentialing record. Clinician retraining + payer re-integration + data migration. Very sticky.</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1749,7 @@
       </c>
       <c r="J25" s="23" t="inlineStr">
         <is>
-          <t>High visibility</t>
+          <t>High visibility. Cloud SaaS established. Mobile/telehealth layered on. AI-assisted notes emerging but additive, not replacement.</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1787,7 @@
       </c>
       <c r="J26" s="23" t="inlineStr">
         <is>
-          <t>Some risk and frequency</t>
+          <t>Regulatory change is mostly tailwind (parity, 42 CFR Part 2, measurement-based care) but adds compliance burden. HIPAA + 50-state licensing variability.</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1825,7 @@
       </c>
       <c r="J27" s="23" t="inlineStr">
         <is>
-          <t>Some liability risks</t>
+          <t>Some liability from HIPAA breaches, incorrect claim submissions, PHI exposure. Manageable with standard safeguards and cyber insurance.</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1863,7 @@
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>Low cyclicality</t>
+          <t>Behavioral health demand counter-cyclical or non-cyclical. Recessions often increase demand. Subscription revenue stable.</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1880,7 @@
       </c>
       <c r="E29" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F29" s="21" t="n"/>
@@ -1838,7 +1901,7 @@
       </c>
       <c r="J29" s="24" t="inlineStr">
         <is>
-          <t>Some resiliency to trends</t>
+          <t>Aligned with durable trends: mental health destigmatization, parity, telehealth, AI documentation. Resilient.</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1936,7 @@
       </c>
       <c r="E31" s="48" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F31" s="9" t="n"/>
@@ -1894,7 +1957,7 @@
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>No VC-backed companies (only PE-owned)</t>
+          <t>Some VC activity (Mentalyc, Upheal, Blueprint) — mostly AI-native point tools rather than full PM/EHR. Limited VC in core category.</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1995,7 @@
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>High competition</t>
+          <t>High competition. Nearly every major incumbent PE-owned and actively rolling up: SimplePractice (EQT), Qualifacts (Warburg), Valant (Resurgens), Netsmart (TPG/GI), Sunwave (BVP Forge).</t>
         </is>
       </c>
     </row>
@@ -1949,7 +2012,7 @@
       </c>
       <c r="E33" s="48" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F33" s="9" t="n"/>
@@ -1970,7 +2033,7 @@
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>No new entrants</t>
+          <t>Moderate barrier: HIPAA + payer integrations + 50-state compliance. General-purpose EHRs cannot match workflow fit. AI-native entrants launching.</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2068,7 @@
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A for SaaS. Cloud hosting costs declining.</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2106,7 @@
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>Some customer power</t>
+          <t>Group practice buyers have some price sensitivity. Solo clinicians price-shop. Enterprise/VBC customers less so. Switching costs reduce power.</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2144,7 @@
       </c>
       <c r="J36" s="24" t="inlineStr">
         <is>
-          <t>Some substitutes</t>
+          <t>Generic EHRs (Epic, athena, DrChrono) and paper-based workflows are substitutes. Specialty fit usually wins but not guaranteed.</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2179,7 @@
       </c>
       <c r="E38" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F38" s="9" t="n"/>
@@ -2137,7 +2200,7 @@
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>Moderate complexity</t>
+          <t>Simple SaaS businesses. Manageable technical complexity. Most targets clinician-founded with lean ops.</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2217,7 @@
       </c>
       <c r="E39" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F39" s="21" t="n"/>
@@ -2175,7 +2238,7 @@
       </c>
       <c r="J39" s="24" t="inlineStr">
         <is>
-          <t>Some actionable levers</t>
+          <t>Many bootstrapped vendors lack professional sales, marketing, CS, and product management. Clear professionalization levers.</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2273,7 @@
       </c>
       <c r="E41" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -2231,7 +2294,7 @@
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>Neutral impact</t>
+          <t>Net positive: expands access to mental health care, reduces clinician admin burden, improves payer outcomes reporting.</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2311,7 @@
       </c>
       <c r="E42" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F42" s="13" t="n"/>
@@ -2269,7 +2332,7 @@
       </c>
       <c r="J42" s="25" t="inlineStr">
         <is>
-          <t>Neutral externalities</t>
+          <t>Positive externalities: better compliance, measurement-based care, expanded access to underserved populations.</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2348,7 @@
       </c>
       <c r="D43" s="18" t="inlineStr">
         <is>
-          <t>Commentary: N/A</t>
+          <t>Commentary: Strong vertical SaaS fundamentals (margins, recurring, switching costs, tailwinds). Main drag is PE saturation of incumbents and high competitive intensity. Right-to-win requires specialty-vertical wedge (womens health, eating disorders, perinatal, SUD) or clinician-founder credibility. Fast sprint: 15-25 independent targets.</t>
         </is>
       </c>
       <c r="E43" s="18" t="n"/>
